--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434582C6-B063-4A49-AD3C-3E1E14C5AA28}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C281F4E4-604E-4624-A9BC-3B8106A5AD0A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5078,14 +5078,12 @@
     <sheetNames>
       <sheetName val="Panel_de_Control"/>
       <sheetName val="Registro_Transacciones"/>
-      <sheetName val="Soporte de compras"/>
       <sheetName val="Configuracion"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5498,7 +5496,7 @@
       </c>
       <c r="C2" s="69">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>25621.65</v>
+        <v>28026.52</v>
       </c>
       <c r="D2" s="68">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5506,7 +5504,7 @@
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>8153.5</v>
+        <v>5748.630000000001</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5514,15 +5512,15 @@
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>17468.150000000001</v>
+        <v>22277.89</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>8153.5</v>
+        <v>5748.630000000001</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.66367324926656146</v>
+        <v>0.72596618851768979</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5530,7 +5528,7 @@
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>12984.169999999998</v>
+        <v>10579.3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5813,7 +5811,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>29451.65</v>
+        <v>31856.52</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -5821,7 +5819,7 @@
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>23812.25</v>
+        <v>21407.38</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -5829,15 +5827,15 @@
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>5639.4000000000015</v>
+        <v>10449.14</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>23812.25</v>
+        <v>21407.38</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.44594414941941174</v>
+        <v>0.48235765109467477</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -5845,7 +5843,7 @@
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>36591.71</v>
+        <v>34186.839999999997</v>
       </c>
     </row>
   </sheetData>
@@ -5870,28 +5868,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5927,7 +5925,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5977,7 +5975,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6211,6 +6209,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6220,14 +6226,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6247,20 +6245,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6402,32 +6400,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10875,38 +10873,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C281F4E4-604E-4624-A9BC-3B8106A5AD0A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610D58BD-827F-49E0-92A9-C3CEA3358EF0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5496,39 +5496,39 @@
       </c>
       <c r="C2" s="69">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>28026.52</v>
+        <v>27512.659999999996</v>
       </c>
       <c r="D2" s="68">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
-        <v>33775.15</v>
+        <v>38578.26</v>
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>5748.630000000001</v>
+        <v>11065.600000000006</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
-        <v>4830.6699999999983</v>
+        <v>27.559999999997672</v>
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>22277.89</v>
+        <v>16447.05999999999</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>5748.630000000001</v>
+        <v>11065.600000000006</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.72596618851768979</v>
+        <v>0.71265576019367016</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
-        <v>0.87487197526176108</v>
+        <v>0.99928611799982492</v>
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>10579.3</v>
+        <v>11093.160000000003</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5811,39 +5811,39 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>31856.52</v>
+        <v>31342.659999999996</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
-        <v>53263.9</v>
+        <v>58067.01</v>
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>21407.38</v>
+        <v>26724.350000000006</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
-        <v>12779.46</v>
+        <v>7976.3499999999985</v>
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>10449.14</v>
+        <v>4618.3099999999904</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>21407.38</v>
+        <v>26724.350000000006</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.48235765109467477</v>
+        <v>0.47457700516751411</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
-        <v>0.80649894251291876</v>
+        <v>0.87922555727025398</v>
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>34186.839999999997</v>
+        <v>34700.700000000004</v>
       </c>
     </row>
   </sheetData>

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610D58BD-827F-49E0-92A9-C3CEA3358EF0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695C3853-8F2A-40EE-8265-CC2F8EA50D58}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5500,23 +5500,23 @@
       </c>
       <c r="D2" s="68">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
-        <v>38578.26</v>
+        <v>38605.82</v>
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>11065.600000000006</v>
+        <v>11093.160000000003</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
-        <v>27.559999999997672</v>
+        <v>0</v>
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>16447.05999999999</v>
+        <v>16419.499999999993</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>11065.600000000006</v>
+        <v>11093.160000000003</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
-        <v>0.99928611799982492</v>
+        <v>1</v>
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
@@ -5815,23 +5815,23 @@
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
-        <v>58067.01</v>
+        <v>58094.57</v>
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>26724.350000000006</v>
+        <v>26751.910000000003</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
-        <v>7976.3499999999985</v>
+        <v>7948.7900000000009</v>
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>4618.3099999999904</v>
+        <v>4590.7499999999927</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>26724.350000000006</v>
+        <v>26751.910000000003</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
-        <v>0.87922555727025398</v>
+        <v>0.87964285887332205</v>
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
@@ -5868,28 +5868,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5925,7 +5925,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6209,14 +6209,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6226,6 +6218,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6245,20 +6245,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6400,32 +6400,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10873,38 +10873,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695C3853-8F2A-40EE-8265-CC2F8EA50D58}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B617720D-82AF-4536-8DA4-3A6001D00176}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C2" s="69">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>27512.659999999996</v>
+        <v>27830.85</v>
       </c>
       <c r="D2" s="68">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>11093.160000000003</v>
+        <v>10774.970000000001</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5512,15 +5512,15 @@
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>16419.499999999993</v>
+        <v>17055.879999999997</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>11093.160000000003</v>
+        <v>10774.970000000001</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.71265576019367016</v>
+        <v>0.72089778173342778</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>11093.160000000003</v>
+        <v>10774.970000000001</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>31342.659999999996</v>
+        <v>31660.85</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>26751.910000000003</v>
+        <v>26433.72</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -5827,15 +5827,15 @@
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>4590.7499999999927</v>
+        <v>5227.1299999999974</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>26751.910000000003</v>
+        <v>26433.72</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.47457700516751411</v>
+        <v>0.47939490056229722</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>34700.700000000004</v>
+        <v>34382.51</v>
       </c>
     </row>
   </sheetData>
@@ -5868,28 +5868,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5925,7 +5925,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5975,7 +5975,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6209,6 +6209,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6218,14 +6226,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6245,20 +6245,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6400,32 +6400,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10873,38 +10873,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B617720D-82AF-4536-8DA4-3A6001D00176}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1138BAF3-F50A-48D3-AC43-60F1072403E0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="349">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1069,6 +1069,15 @@
   </si>
   <si>
     <t>FLUJO DE CAJA</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>CULMINADA</t>
+  </si>
+  <si>
+    <t>ACTIVA</t>
   </si>
 </sst>
 </file>
@@ -1522,13 +1531,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5079,11 +5088,13 @@
       <sheetName val="Panel_de_Control"/>
       <sheetName val="Registro_Transacciones"/>
       <sheetName val="Configuracion"/>
+      <sheetName val="Control Obras"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5435,7 +5446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8E136-486C-4EB9-920D-6287CDC3043B}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="32" bestFit="1" customWidth="1"/>
@@ -5451,7 +5462,7 @@
     <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>334</v>
       </c>
@@ -5485,8 +5496,11 @@
       <c r="K1" s="32" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="32" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
         <v>335</v>
       </c>
@@ -5530,8 +5544,11 @@
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
         <v>10774.970000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
         <v>336</v>
       </c>
@@ -5575,8 +5592,11 @@
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="71" t="s">
         <v>337</v>
       </c>
@@ -5620,8 +5640,11 @@
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
         <v>338</v>
       </c>
@@ -5665,8 +5688,11 @@
         <f t="shared" si="5"/>
         <v>7324</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="71" t="s">
         <v>339</v>
       </c>
@@ -5710,8 +5736,11 @@
         <f t="shared" si="5"/>
         <v>5525</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
         <v>340</v>
       </c>
@@ -5755,8 +5784,11 @@
         <f t="shared" si="5"/>
         <v>1743.75</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="71" t="s">
         <v>341</v>
       </c>
@@ -5800,8 +5832,11 @@
         <f t="shared" si="5"/>
         <v>8484.7900000000009</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
         <v>342</v>
       </c>
@@ -5844,6 +5879,9 @@
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
         <v>34382.51</v>
+      </c>
+      <c r="L9" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -5868,28 +5906,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5925,7 +5963,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5975,7 +6013,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6209,14 +6247,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6226,6 +6256,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6245,20 +6283,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6400,32 +6438,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10873,38 +10911,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1138BAF3-F50A-48D3-AC43-60F1072403E0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FED2218-7C8B-4F06-8DBA-BE69AE9094A8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1531,13 +1531,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5906,28 +5906,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5963,7 +5963,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6013,7 +6013,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6247,6 +6247,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6256,14 +6264,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6283,20 +6283,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6438,32 +6438,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10911,38 +10911,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FED2218-7C8B-4F06-8DBA-BE69AE9094A8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5006E0E-3D84-4AAF-8674-713077CCB522}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1531,13 +1531,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5460,6 +5460,7 @@
     <col min="9" max="9" width="18.7109375" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.140625" style="72" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -5906,28 +5907,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5963,7 +5964,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6013,7 +6014,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6247,14 +6248,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6264,6 +6257,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6283,20 +6284,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6438,32 +6439,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10911,38 +10912,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5006E0E-3D84-4AAF-8674-713077CCB522}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E8C9D0-A169-49BB-95C7-6438002A0007}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1531,13 +1531,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5907,28 +5907,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5964,7 +5964,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6248,6 +6248,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6257,14 +6265,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6284,20 +6284,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6439,32 +6439,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10912,38 +10912,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E8C9D0-A169-49BB-95C7-6438002A0007}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C479F596-0897-4F69-B5B8-6A2119A50E51}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="349">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1023,9 +1023,6 @@
     <t>Utilidad Bruta</t>
   </si>
   <si>
-    <t>Flujo de Caja</t>
-  </si>
-  <si>
     <t>% Avance Facturado</t>
   </si>
   <si>
@@ -1078,6 +1075,9 @@
   </si>
   <si>
     <t>ACTIVA</t>
+  </si>
+  <si>
+    <t>Flujo de Caja2</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1335,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1531,11 +1531,14 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1545,7 +1548,351 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="52">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -5088,74 +5435,107 @@
       <sheetName val="Panel_de_Control"/>
       <sheetName val="Registro_Transacciones"/>
       <sheetName val="Configuracion"/>
-      <sheetName val="Control Obras"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
-  <autoFilter ref="A4:E10" xr:uid="{8ABC211C-7D80-490C-9B76-89253396DB9F}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L10" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:L10" xr:uid="{A4D9C4A4-4BEE-43F7-B482-6B69DD695700}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="7">
+      <calculatedColumnFormula>D2-C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="6">
+      <calculatedColumnFormula>B2-D2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="5">
+      <calculatedColumnFormula>C2-E2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="4">
+      <calculatedColumnFormula>E2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="3" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="2" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula>D2/B2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="1">
+      <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
-  <autoFilter ref="A4:M119" xr:uid="{C3432B77-315D-40F3-A17B-615A4A292D9C}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="21" dataCellStyle="Millares">
-      <calculatedColumnFormula>Tabla4[[#This Row],[Cantidad]]*Tabla4[[#This Row],[Precio Unitario Bs]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+  <autoFilter ref="A4:E10" xr:uid="{8ABC211C-7D80-490C-9B76-89253396DB9F}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="45"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
+  <autoFilter ref="A4:M119" xr:uid="{C3432B77-315D-40F3-A17B-615A4A292D9C}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="33" dataCellStyle="Millares">
+      <calculatedColumnFormula>Tabla4[[#This Row],[Cantidad]]*Tabla4[[#This Row],[Precio Unitario Bs]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="29"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="A4:N46" xr:uid="{EA34636B-E6DC-4743-A5C0-1FA27FABC114}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="8" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="7" dataCellStyle="Millares"/>
-    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="5" dataCellStyle="Millares"/>
-    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="20" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5446,38 +5826,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8E136-486C-4EB9-920D-6287CDC3043B}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="32" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="32"/>
-    <col min="7" max="7" width="13.140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="32" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="32" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" style="32" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.140625" style="72" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" style="32" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="72" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" customWidth="1"/>
     <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>327</v>
       </c>
       <c r="C1" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="E1" s="32" t="s">
         <v>344</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>345</v>
       </c>
       <c r="F1" s="32" t="s">
         <v>328</v>
@@ -5486,24 +5866,24 @@
         <v>329</v>
       </c>
       <c r="H1" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="I1" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="J1" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="J1" s="72" t="s">
+      <c r="K1" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="K1" s="32" t="s">
-        <v>333</v>
-      </c>
       <c r="L1" s="32" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B2" s="68">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
@@ -5518,7 +5898,7 @@
         <v>38605.82</v>
       </c>
       <c r="E2" s="68">
-        <f t="shared" ref="E2:E8" si="0">D2-C2</f>
+        <f t="shared" ref="E2:E9" si="0">D2-C2</f>
         <v>10774.970000000001</v>
       </c>
       <c r="F2" s="68">
@@ -5534,24 +5914,24 @@
         <v>10774.970000000001</v>
       </c>
       <c r="I2" s="72">
-        <f t="shared" ref="I2:I8" si="3">C2/B2</f>
+        <f t="shared" ref="I2:I9" si="3">C2/B2</f>
         <v>0.72089778173342778</v>
       </c>
       <c r="J2" s="72">
-        <f t="shared" ref="J2:J8" si="4">D2/B2</f>
+        <f t="shared" ref="J2:J9" si="4">D2/B2</f>
         <v>1</v>
       </c>
       <c r="K2" s="68">
-        <f t="shared" ref="K2:K8" si="5">B2-C2</f>
+        <f t="shared" ref="K2:K9" si="5">B2-C2</f>
         <v>10774.970000000001</v>
       </c>
       <c r="L2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B3" s="68">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
@@ -5594,12 +5974,12 @@
         <v>265</v>
       </c>
       <c r="L3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="71" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B4" s="68">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
@@ -5642,12 +6022,12 @@
         <v>265</v>
       </c>
       <c r="L4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B5" s="68">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
@@ -5666,11 +6046,11 @@
         <v>3114</v>
       </c>
       <c r="F5" s="68">
-        <f t="shared" ref="F5:F8" si="6">B5-D5</f>
+        <f t="shared" ref="F5:F9" si="6">B5-D5</f>
         <v>4210</v>
       </c>
       <c r="G5" s="68">
-        <f t="shared" ref="G5:G8" si="7">C5-E5</f>
+        <f t="shared" ref="G5:G9" si="7">C5-E5</f>
         <v>86</v>
       </c>
       <c r="H5" s="68">
@@ -5690,12 +6070,12 @@
         <v>7324</v>
       </c>
       <c r="L5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B6" s="68">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
@@ -5738,12 +6118,12 @@
         <v>5525</v>
       </c>
       <c r="L6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B7" s="68">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
@@ -5786,12 +6166,12 @@
         <v>1743.75</v>
       </c>
       <c r="L7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="71" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B8" s="68">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
@@ -5834,60 +6214,106 @@
         <v>8484.7900000000009</v>
       </c>
       <c r="L8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
-        <v>342</v>
-      </c>
-      <c r="B9" s="73">
-        <f>SUM(B2:B8)</f>
-        <v>66043.360000000001</v>
-      </c>
-      <c r="C9" s="73">
-        <f>SUM(C2:C8)</f>
+        <v>325</v>
+      </c>
+      <c r="B9" s="80">
+        <v>15000</v>
+      </c>
+      <c r="C9" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="80">
+        <v>5000</v>
+      </c>
+      <c r="E9" s="68">
+        <f t="shared" si="0"/>
+        <v>5000</v>
+      </c>
+      <c r="F9" s="68">
+        <f t="shared" si="6"/>
+        <v>10000</v>
+      </c>
+      <c r="G9" s="68">
+        <f t="shared" si="7"/>
+        <v>-5000</v>
+      </c>
+      <c r="H9" s="68"/>
+      <c r="I9" s="72">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="72">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K9" s="68">
+        <f t="shared" si="5"/>
+        <v>15000</v>
+      </c>
+      <c r="L9" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="71" t="s">
+        <v>341</v>
+      </c>
+      <c r="B10" s="73">
+        <f>SUM(B2:B9)</f>
+        <v>81043.360000000001</v>
+      </c>
+      <c r="C10" s="73">
+        <f>SUM(C2:C9)</f>
         <v>31660.85</v>
       </c>
-      <c r="D9" s="73">
-        <f>SUM(D2:D8)</f>
-        <v>58094.57</v>
-      </c>
-      <c r="E9" s="68">
-        <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>26433.72</v>
-      </c>
-      <c r="F9" s="68">
-        <f t="shared" ref="F9" si="9">B9-D9</f>
-        <v>7948.7900000000009</v>
-      </c>
-      <c r="G9" s="68">
-        <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>5227.1299999999974</v>
-      </c>
-      <c r="H9" s="68">
-        <f t="shared" ref="H9" si="11">E9</f>
-        <v>26433.72</v>
-      </c>
-      <c r="I9" s="72">
-        <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.47939490056229722</v>
-      </c>
-      <c r="J9" s="72">
-        <f t="shared" ref="J9" si="13">D9/B9</f>
-        <v>0.87964285887332205</v>
-      </c>
-      <c r="K9" s="68">
-        <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>34382.51</v>
-      </c>
-      <c r="L9" t="s">
-        <v>348</v>
+      <c r="D10" s="73">
+        <f>SUM(D2:D9)</f>
+        <v>63094.57</v>
+      </c>
+      <c r="E10" s="68">
+        <f t="shared" ref="E10" si="8">D10-C10</f>
+        <v>31433.72</v>
+      </c>
+      <c r="F10" s="68">
+        <f t="shared" ref="F10" si="9">B10-D10</f>
+        <v>17948.79</v>
+      </c>
+      <c r="G10" s="68">
+        <f t="shared" ref="G10" si="10">C10-E10</f>
+        <v>227.12999999999738</v>
+      </c>
+      <c r="H10" s="68">
+        <f t="shared" ref="H10" si="11">E10</f>
+        <v>31433.72</v>
+      </c>
+      <c r="I10" s="72">
+        <f t="shared" ref="I10" si="12">C10/B10</f>
+        <v>0.39066556470511588</v>
+      </c>
+      <c r="J10" s="72">
+        <f t="shared" ref="J10" si="13">D10/B10</f>
+        <v>0.77852855557814982</v>
+      </c>
+      <c r="K10" s="68">
+        <f t="shared" ref="K10" si="14">B10-C10</f>
+        <v>49382.51</v>
+      </c>
+      <c r="L10" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5907,28 +6333,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5964,7 +6390,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6014,7 +6440,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6248,14 +6674,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6265,6 +6683,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6284,20 +6710,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6439,32 +6865,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10912,38 +11338,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C479F596-0897-4F69-B5B8-6A2119A50E51}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2308045-117B-4667-8072-250E361565E3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="349">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1335,7 +1335,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1506,22 +1506,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1531,15 +1519,31 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1548,8 +1552,122 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="54">
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1570,8 +1688,14 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCBD5E1"/>
         </left>
@@ -1584,84 +1708,6 @@
         <bottom style="thin">
           <color rgb="FFCBD5E1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1682,8 +1728,14 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCBD5E1"/>
         </left>
@@ -1696,8 +1748,6 @@
         <bottom style="thin">
           <color rgb="FFCBD5E1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1718,8 +1768,14 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCBD5E1"/>
         </left>
@@ -1732,8 +1788,6 @@
         <bottom style="thin">
           <color rgb="FFCBD5E1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1754,8 +1808,14 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCBD5E1"/>
         </left>
@@ -1768,8 +1828,6 @@
         <bottom style="thin">
           <color rgb="FFCBD5E1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1790,8 +1848,14 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCBD5E1"/>
         </left>
@@ -1804,8 +1868,6 @@
         <bottom style="thin">
           <color rgb="FFCBD5E1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1826,16 +1888,20 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
         <top style="thin">
           <color rgb="FFCBD5E1"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1856,8 +1922,14 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFCBD5E1"/>
         </left>
@@ -1870,8 +1942,6 @@
         <bottom style="thin">
           <color rgb="FFCBD5E1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1891,6 +1961,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -5446,96 +5522,96 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L10" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:L10" xr:uid="{A4D9C4A4-4BEE-43F7-B482-6B69DD695700}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:L9" xr:uid="{A4D9C4A4-4BEE-43F7-B482-6B69DD695700}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="9">
       <calculatedColumnFormula>D2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="6">
+    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="8">
       <calculatedColumnFormula>B2-D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="5">
+    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="7">
       <calculatedColumnFormula>C2-E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="4">
+    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="6">
       <calculatedColumnFormula>E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="3" dataCellStyle="Porcentaje">
+    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="5" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="2" dataCellStyle="Porcentaje">
+    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="4" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>D2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="3">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado"/>
+    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A4:E10" xr:uid="{8ABC211C-7D80-490C-9B76-89253396DB9F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
   <autoFilter ref="A4:M119" xr:uid="{C3432B77-315D-40F3-A17B-615A4A292D9C}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="33" dataCellStyle="Millares">
+    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="35" dataCellStyle="Millares">
       <calculatedColumnFormula>Tabla4[[#This Row],[Cantidad]]*Tabla4[[#This Row],[Precio Unitario Bs]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
   <autoFilter ref="A4:N46" xr:uid="{EA34636B-E6DC-4743-A5C0-1FA27FABC114}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="20" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5826,485 +5902,442 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8E136-486C-4EB9-920D-6287CDC3043B}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" style="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="32" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" style="32" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" style="32" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" style="32" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="32" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" style="32" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" style="32" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="72" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="69" customWidth="1"/>
     <col min="11" max="11" width="19.140625" customWidth="1"/>
     <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="76" t="s">
         <v>333</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="76" t="s">
         <v>327</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="76" t="s">
         <v>342</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="76" t="s">
         <v>343</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="76" t="s">
         <v>344</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="76" t="s">
         <v>328</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="76" t="s">
         <v>329</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="76" t="s">
         <v>348</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="76" t="s">
         <v>330</v>
       </c>
-      <c r="J1" s="72" t="s">
+      <c r="J1" s="77" t="s">
         <v>331</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="76" t="s">
         <v>332</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="76" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="78" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="68">
+      <c r="B2" s="79">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>38605.82</v>
       </c>
-      <c r="C2" s="69">
+      <c r="C2" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>27830.85</v>
-      </c>
-      <c r="D2" s="68">
+        <v>27891.969999999994</v>
+      </c>
+      <c r="D2" s="79">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>38605.82</v>
       </c>
-      <c r="E2" s="68">
-        <f t="shared" ref="E2:E9" si="0">D2-C2</f>
-        <v>10774.970000000001</v>
-      </c>
-      <c r="F2" s="68">
+      <c r="E2" s="79">
+        <f t="shared" ref="E2:E8" si="0">D2-C2</f>
+        <v>10713.850000000006</v>
+      </c>
+      <c r="F2" s="79">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="68">
+      <c r="G2" s="79">
         <f t="shared" si="1"/>
-        <v>17055.879999999997</v>
-      </c>
-      <c r="H2" s="68">
+        <v>17178.119999999988</v>
+      </c>
+      <c r="H2" s="79">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>10774.970000000001</v>
-      </c>
-      <c r="I2" s="72">
-        <f t="shared" ref="I2:I9" si="3">C2/B2</f>
-        <v>0.72089778173342778</v>
-      </c>
-      <c r="J2" s="72">
-        <f t="shared" ref="J2:J9" si="4">D2/B2</f>
+        <v>10713.850000000006</v>
+      </c>
+      <c r="I2" s="77">
+        <f t="shared" ref="I2:I8" si="3">C2/B2</f>
+        <v>0.72248096271494799</v>
+      </c>
+      <c r="J2" s="77">
+        <f t="shared" ref="J2:J8" si="4">D2/B2</f>
         <v>1</v>
       </c>
-      <c r="K2" s="68">
-        <f t="shared" ref="K2:K9" si="5">B2-C2</f>
-        <v>10774.970000000001</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="K2" s="79">
+        <f t="shared" ref="K2:K8" si="5">B2-C2</f>
+        <v>10713.850000000006</v>
+      </c>
+      <c r="L2" s="81" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="78" t="s">
         <v>335</v>
       </c>
-      <c r="B3" s="68">
+      <c r="B3" s="79">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C3" s="69">
+      <c r="C3" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D3" s="68">
+      <c r="D3" s="79">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E3" s="68">
+      <c r="E3" s="79">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F3" s="68">
+      <c r="F3" s="79">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G3" s="68">
+      <c r="G3" s="79">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H3" s="68">
+      <c r="H3" s="79">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="I3" s="72">
+      <c r="I3" s="77">
         <f t="shared" si="3"/>
         <v>0.5431034482758621</v>
       </c>
-      <c r="J3" s="72">
+      <c r="J3" s="77">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K3" s="68">
+      <c r="K3" s="79">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="81" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="78" t="s">
         <v>336</v>
       </c>
-      <c r="B4" s="68">
+      <c r="B4" s="79">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D4" s="68">
+      <c r="D4" s="79">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E4" s="68">
+      <c r="E4" s="79">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F4" s="68">
+      <c r="F4" s="79">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G4" s="68">
+      <c r="G4" s="79">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H4" s="68">
+      <c r="H4" s="79">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="I4" s="72">
+      <c r="I4" s="77">
         <f t="shared" si="3"/>
         <v>0.5431034482758621</v>
       </c>
-      <c r="J4" s="72">
+      <c r="J4" s="77">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K4" s="68">
+      <c r="K4" s="79">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="81" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="78" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="68">
+      <c r="B5" s="79">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>10524</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>3200</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>6314</v>
       </c>
-      <c r="E5" s="68">
+      <c r="E5" s="79">
         <f t="shared" si="0"/>
         <v>3114</v>
       </c>
-      <c r="F5" s="68">
-        <f t="shared" ref="F5:F9" si="6">B5-D5</f>
+      <c r="F5" s="79">
+        <f t="shared" ref="F5:F8" si="6">B5-D5</f>
         <v>4210</v>
       </c>
-      <c r="G5" s="68">
-        <f t="shared" ref="G5:G9" si="7">C5-E5</f>
+      <c r="G5" s="79">
+        <f t="shared" ref="G5:G8" si="7">C5-E5</f>
         <v>86</v>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="79">
         <f t="shared" si="2"/>
         <v>3114</v>
       </c>
-      <c r="I5" s="72">
+      <c r="I5" s="77">
         <f t="shared" si="3"/>
         <v>0.30406689471683768</v>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="77">
         <f t="shared" si="4"/>
         <v>0.59996199163816044</v>
       </c>
-      <c r="K5" s="68">
+      <c r="K5" s="79">
         <f t="shared" si="5"/>
         <v>7324</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="81" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="78" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="68">
+      <c r="B6" s="79">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>5525</v>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
-      <c r="D6" s="68">
+      <c r="D6" s="79">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5525</v>
       </c>
-      <c r="E6" s="68">
+      <c r="E6" s="79">
         <f t="shared" si="0"/>
         <v>5525</v>
       </c>
-      <c r="F6" s="68">
+      <c r="F6" s="79">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G6" s="68">
+      <c r="G6" s="79">
         <f t="shared" si="7"/>
         <v>-5525</v>
       </c>
-      <c r="H6" s="68">
+      <c r="H6" s="79">
         <f t="shared" si="2"/>
         <v>5525</v>
       </c>
-      <c r="I6" s="72">
+      <c r="I6" s="77">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J6" s="72">
+      <c r="J6" s="77">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K6" s="68">
+      <c r="K6" s="79">
         <f t="shared" si="5"/>
         <v>5525</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="81" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="78" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="68">
+      <c r="B7" s="79">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>1743.75</v>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
-      <c r="D7" s="68">
+      <c r="D7" s="79">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>1743.75</v>
       </c>
-      <c r="E7" s="68">
+      <c r="E7" s="79">
         <f t="shared" si="0"/>
         <v>1743.75</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="79">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G7" s="68">
+      <c r="G7" s="79">
         <f t="shared" si="7"/>
         <v>-1743.75</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="79">
         <f t="shared" si="2"/>
         <v>1743.75</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="77">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="77">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="79">
         <f t="shared" si="5"/>
         <v>1743.75</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="81" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="78" t="s">
         <v>340</v>
       </c>
-      <c r="B8" s="68">
+      <c r="B8" s="79">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>8484.7900000000009</v>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="80">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
-      <c r="D8" s="68">
+      <c r="D8" s="79">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5094</v>
       </c>
-      <c r="E8" s="68">
+      <c r="E8" s="79">
         <f t="shared" si="0"/>
         <v>5094</v>
       </c>
-      <c r="F8" s="68">
+      <c r="F8" s="79">
         <f t="shared" si="6"/>
         <v>3390.7900000000009</v>
       </c>
-      <c r="G8" s="68">
+      <c r="G8" s="79">
         <f t="shared" si="7"/>
         <v>-5094</v>
       </c>
-      <c r="H8" s="68">
+      <c r="H8" s="79">
         <f t="shared" si="2"/>
         <v>5094</v>
       </c>
-      <c r="I8" s="72">
+      <c r="I8" s="77">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J8" s="72">
+      <c r="J8" s="77">
         <f t="shared" si="4"/>
         <v>0.60036842396806511</v>
       </c>
-      <c r="K8" s="68">
+      <c r="K8" s="79">
         <f t="shared" si="5"/>
         <v>8484.7900000000009</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="81" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
-        <v>325</v>
-      </c>
-      <c r="B9" s="80">
-        <v>15000</v>
-      </c>
-      <c r="C9" s="69">
-        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="80">
-        <v>5000</v>
-      </c>
-      <c r="E9" s="68">
-        <f t="shared" si="0"/>
-        <v>5000</v>
-      </c>
-      <c r="F9" s="68">
-        <f t="shared" si="6"/>
-        <v>10000</v>
-      </c>
-      <c r="G9" s="68">
-        <f t="shared" si="7"/>
-        <v>-5000</v>
-      </c>
-      <c r="H9" s="68"/>
-      <c r="I9" s="72">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J9" s="72">
-        <f t="shared" si="4"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="K9" s="68">
-        <f t="shared" si="5"/>
-        <v>15000</v>
-      </c>
-      <c r="L9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
+      <c r="A9" s="78" t="s">
         <v>341</v>
       </c>
-      <c r="B10" s="73">
-        <f>SUM(B2:B9)</f>
-        <v>81043.360000000001</v>
-      </c>
-      <c r="C10" s="73">
-        <f>SUM(C2:C9)</f>
-        <v>31660.85</v>
-      </c>
-      <c r="D10" s="73">
-        <f>SUM(D2:D9)</f>
-        <v>63094.57</v>
-      </c>
-      <c r="E10" s="68">
-        <f t="shared" ref="E10" si="8">D10-C10</f>
-        <v>31433.72</v>
-      </c>
-      <c r="F10" s="68">
-        <f t="shared" ref="F10" si="9">B10-D10</f>
-        <v>17948.79</v>
-      </c>
-      <c r="G10" s="68">
-        <f t="shared" ref="G10" si="10">C10-E10</f>
-        <v>227.12999999999738</v>
-      </c>
-      <c r="H10" s="68">
-        <f t="shared" ref="H10" si="11">E10</f>
-        <v>31433.72</v>
-      </c>
-      <c r="I10" s="72">
-        <f t="shared" ref="I10" si="12">C10/B10</f>
-        <v>0.39066556470511588</v>
-      </c>
-      <c r="J10" s="72">
-        <f t="shared" ref="J10" si="13">D10/B10</f>
-        <v>0.77852855557814982</v>
-      </c>
-      <c r="K10" s="68">
-        <f t="shared" ref="K10" si="14">B10-C10</f>
-        <v>49382.51</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="B9" s="82">
+        <f>SUM(B2:B8)</f>
+        <v>66043.360000000001</v>
+      </c>
+      <c r="C9" s="82">
+        <f>SUM(C2:C8)</f>
+        <v>31721.969999999994</v>
+      </c>
+      <c r="D9" s="82">
+        <f>SUM(D2:D8)</f>
+        <v>58094.57</v>
+      </c>
+      <c r="E9" s="79">
+        <f t="shared" ref="E9" si="8">D9-C9</f>
+        <v>26372.600000000006</v>
+      </c>
+      <c r="F9" s="79">
+        <f t="shared" ref="F9" si="9">B9-D9</f>
+        <v>7948.7900000000009</v>
+      </c>
+      <c r="G9" s="79">
+        <f t="shared" ref="G9" si="10">C9-E9</f>
+        <v>5349.3699999999881</v>
+      </c>
+      <c r="H9" s="79">
+        <f t="shared" ref="H9" si="11">E9</f>
+        <v>26372.600000000006</v>
+      </c>
+      <c r="I9" s="77">
+        <f t="shared" ref="I9" si="12">C9/B9</f>
+        <v>0.48032035317403587</v>
+      </c>
+      <c r="J9" s="77">
+        <f t="shared" ref="J9" si="13">D9/B9</f>
+        <v>0.87964285887332205</v>
+      </c>
+      <c r="K9" s="79">
+        <f t="shared" ref="K9" si="14">B9-C9</f>
+        <v>34321.390000000007</v>
+      </c>
+      <c r="L9" s="81" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6333,128 +6366,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="74" t="s">
+      <c r="A4" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="71"/>
+      <c r="C4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="75"/>
-      <c r="E4" s="74" t="s">
+      <c r="D4" s="71"/>
+      <c r="E4" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="74" t="s">
+      <c r="F4" s="71"/>
+      <c r="G4" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="75"/>
+      <c r="H4" s="71"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="76">
+      <c r="A5" s="72">
         <f>Presupuesto!E11</f>
         <v>43821.59</v>
       </c>
-      <c r="B5" s="75"/>
-      <c r="C5" s="76">
+      <c r="B5" s="71"/>
+      <c r="C5" s="72">
         <f>Compras_Materiales!L120+Pago_Obreros!M47</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D5" s="75"/>
-      <c r="E5" s="76">
+      <c r="D5" s="71"/>
+      <c r="E5" s="72">
         <f>A5-C5</f>
         <v>22037.563618134853</v>
       </c>
-      <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="F5" s="71"/>
+      <c r="G5" s="75">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
-      <c r="H5" s="75"/>
+      <c r="H5" s="71"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="75"/>
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="70" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="74" t="s">
+      <c r="B7" s="71"/>
+      <c r="C7" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="75"/>
-      <c r="E7" s="74" t="s">
+      <c r="D7" s="71"/>
+      <c r="E7" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="75"/>
-      <c r="G7" s="74" t="s">
+      <c r="F7" s="71"/>
+      <c r="G7" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="75"/>
+      <c r="H7" s="71"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="76">
+      <c r="A8" s="72">
         <f>B23</f>
         <v>33203.99</v>
       </c>
-      <c r="B8" s="75"/>
-      <c r="C8" s="76">
+      <c r="B8" s="71"/>
+      <c r="C8" s="72">
         <f>C14</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D8" s="75"/>
-      <c r="E8" s="76">
+      <c r="D8" s="71"/>
+      <c r="E8" s="72">
         <f>A8-C8</f>
         <v>11419.963618134854</v>
       </c>
-      <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="F8" s="71"/>
+      <c r="G8" s="75">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
-      <c r="H8" s="75"/>
+      <c r="H8" s="71"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="75"/>
-      <c r="B9" s="75"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
+      <c r="A9" s="71"/>
+      <c r="B9" s="71"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -6623,7 +6656,7 @@
       <c r="B21" s="6">
         <v>22586.39</v>
       </c>
-      <c r="C21" s="70">
+      <c r="C21" s="68">
         <v>1</v>
       </c>
       <c r="D21" s="6">
@@ -6640,7 +6673,7 @@
       <c r="B22" s="6">
         <v>10617.6</v>
       </c>
-      <c r="C22" s="70">
+      <c r="C22" s="68">
         <v>0.5</v>
       </c>
       <c r="D22" s="6">
@@ -6674,6 +6707,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6683,14 +6724,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6710,20 +6743,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6865,32 +6898,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="73" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11338,38 +11371,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="74"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2308045-117B-4667-8072-250E361565E3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D356644D-56A4-400B-A8B1-6A6FE3D380E0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1335,7 +1335,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1512,6 +1512,21 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1526,25 +1541,6 @@
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -1553,422 +1549,6 @@
     <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="54">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF1E293B"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3060,6 +2640,422 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5522,96 +5518,96 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A1:L9" xr:uid="{A4D9C4A4-4BEE-43F7-B482-6B69DD695700}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="47">
       <calculatedColumnFormula>D2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="8">
+    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="46">
       <calculatedColumnFormula>B2-D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="7">
+    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="45">
       <calculatedColumnFormula>C2-E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="6">
+    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="44">
       <calculatedColumnFormula>E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="5" dataCellStyle="Porcentaje">
+    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="43" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="4" dataCellStyle="Porcentaje">
+    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="42" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>D2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="3">
+    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="41">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A4:E10" xr:uid="{8ABC211C-7D80-490C-9B76-89253396DB9F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A4:M119" xr:uid="{C3432B77-315D-40F3-A17B-615A4A292D9C}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="36" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="35" dataCellStyle="Millares">
+    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="21" dataCellStyle="Millares">
       <calculatedColumnFormula>Tabla4[[#This Row],[Cantidad]]*Tabla4[[#This Row],[Precio Unitario Bs]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A4:N46" xr:uid="{EA34636B-E6DC-4743-A5C0-1FA27FABC114}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="7" dataCellStyle="Millares"/>
+    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="5" dataCellStyle="Millares"/>
+    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5920,424 +5916,424 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="32" t="s">
         <v>333</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="32" t="s">
         <v>327</v>
       </c>
-      <c r="C1" s="76" t="s">
+      <c r="C1" s="32" t="s">
         <v>342</v>
       </c>
-      <c r="D1" s="76" t="s">
+      <c r="D1" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="E1" s="76" t="s">
+      <c r="E1" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="G1" s="76" t="s">
+      <c r="G1" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="H1" s="76" t="s">
+      <c r="H1" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="J1" s="77" t="s">
+      <c r="J1" s="70" t="s">
         <v>331</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="L1" s="76" t="s">
+      <c r="L1" s="32" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="71" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="79">
+      <c r="B2" s="72">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>38605.82</v>
       </c>
-      <c r="C2" s="80">
+      <c r="C2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>27891.969999999994</v>
-      </c>
-      <c r="D2" s="79">
+        <v>28086.599999999995</v>
+      </c>
+      <c r="D2" s="72">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>38605.82</v>
       </c>
-      <c r="E2" s="79">
+      <c r="E2" s="72">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>10713.850000000006</v>
-      </c>
-      <c r="F2" s="79">
+        <v>10519.220000000005</v>
+      </c>
+      <c r="F2" s="72">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="79">
+      <c r="G2" s="72">
         <f t="shared" si="1"/>
-        <v>17178.119999999988</v>
-      </c>
-      <c r="H2" s="79">
+        <v>17567.37999999999</v>
+      </c>
+      <c r="H2" s="72">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>10713.850000000006</v>
-      </c>
-      <c r="I2" s="77">
+        <v>10519.220000000005</v>
+      </c>
+      <c r="I2" s="70">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.72248096271494799</v>
-      </c>
-      <c r="J2" s="77">
+        <v>0.72752243055580723</v>
+      </c>
+      <c r="J2" s="70">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
         <v>1</v>
       </c>
-      <c r="K2" s="79">
+      <c r="K2" s="72">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>10713.850000000006</v>
-      </c>
-      <c r="L2" s="81" t="s">
+        <v>10519.220000000005</v>
+      </c>
+      <c r="L2" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="71" t="s">
         <v>335</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="72">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C3" s="80">
+      <c r="C3" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D3" s="79">
+      <c r="D3" s="72">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E3" s="79">
+      <c r="E3" s="72">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F3" s="79">
+      <c r="F3" s="72">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G3" s="79">
+      <c r="G3" s="72">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H3" s="79">
+      <c r="H3" s="72">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="I3" s="77">
+      <c r="I3" s="70">
         <f t="shared" si="3"/>
         <v>0.5431034482758621</v>
       </c>
-      <c r="J3" s="77">
+      <c r="J3" s="70">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K3" s="79">
+      <c r="K3" s="72">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L3" s="81" t="s">
+      <c r="L3" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="71" t="s">
         <v>336</v>
       </c>
-      <c r="B4" s="79">
+      <c r="B4" s="72">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C4" s="80">
+      <c r="C4" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="72">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E4" s="79">
+      <c r="E4" s="72">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F4" s="79">
+      <c r="F4" s="72">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G4" s="79">
+      <c r="G4" s="72">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H4" s="79">
+      <c r="H4" s="72">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
-      <c r="I4" s="77">
+      <c r="I4" s="70">
         <f t="shared" si="3"/>
         <v>0.5431034482758621</v>
       </c>
-      <c r="J4" s="77">
+      <c r="J4" s="70">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K4" s="79">
+      <c r="K4" s="72">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L4" s="81" t="s">
+      <c r="L4" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="71" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="79">
+      <c r="B5" s="72">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>10524</v>
       </c>
-      <c r="C5" s="80">
+      <c r="C5" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>3200</v>
-      </c>
-      <c r="D5" s="80">
+        <v>3236.5699999999997</v>
+      </c>
+      <c r="D5" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>6314</v>
       </c>
-      <c r="E5" s="79">
+      <c r="E5" s="72">
         <f t="shared" si="0"/>
-        <v>3114</v>
-      </c>
-      <c r="F5" s="79">
+        <v>3077.4300000000003</v>
+      </c>
+      <c r="F5" s="72">
         <f t="shared" ref="F5:F8" si="6">B5-D5</f>
         <v>4210</v>
       </c>
-      <c r="G5" s="79">
+      <c r="G5" s="72">
         <f t="shared" ref="G5:G8" si="7">C5-E5</f>
-        <v>86</v>
-      </c>
-      <c r="H5" s="79">
+        <v>159.13999999999942</v>
+      </c>
+      <c r="H5" s="72">
         <f t="shared" si="2"/>
-        <v>3114</v>
-      </c>
-      <c r="I5" s="77">
+        <v>3077.4300000000003</v>
+      </c>
+      <c r="I5" s="70">
         <f t="shared" si="3"/>
-        <v>0.30406689471683768</v>
-      </c>
-      <c r="J5" s="77">
+        <v>0.30754180919802354</v>
+      </c>
+      <c r="J5" s="70">
         <f t="shared" si="4"/>
         <v>0.59996199163816044</v>
       </c>
-      <c r="K5" s="79">
+      <c r="K5" s="72">
         <f t="shared" si="5"/>
-        <v>7324</v>
-      </c>
-      <c r="L5" s="81" t="s">
+        <v>7287.43</v>
+      </c>
+      <c r="L5" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="71" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="79">
+      <c r="B6" s="72">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>5525</v>
       </c>
-      <c r="C6" s="80">
+      <c r="C6" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="79">
+        <v>276.25</v>
+      </c>
+      <c r="D6" s="72">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5525</v>
       </c>
-      <c r="E6" s="79">
+      <c r="E6" s="72">
         <f t="shared" si="0"/>
-        <v>5525</v>
-      </c>
-      <c r="F6" s="79">
+        <v>5248.75</v>
+      </c>
+      <c r="F6" s="72">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G6" s="79">
+      <c r="G6" s="72">
         <f t="shared" si="7"/>
-        <v>-5525</v>
-      </c>
-      <c r="H6" s="79">
+        <v>-4972.5</v>
+      </c>
+      <c r="H6" s="72">
         <f t="shared" si="2"/>
-        <v>5525</v>
-      </c>
-      <c r="I6" s="77">
+        <v>5248.75</v>
+      </c>
+      <c r="I6" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="77">
+        <v>0.05</v>
+      </c>
+      <c r="J6" s="70">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K6" s="79">
+      <c r="K6" s="72">
         <f t="shared" si="5"/>
-        <v>5525</v>
-      </c>
-      <c r="L6" s="81" t="s">
+        <v>5248.75</v>
+      </c>
+      <c r="L6" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="71" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="79">
+      <c r="B7" s="72">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>1743.75</v>
       </c>
-      <c r="C7" s="80">
+      <c r="C7" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="79">
+        <v>87.18</v>
+      </c>
+      <c r="D7" s="72">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>1743.75</v>
       </c>
-      <c r="E7" s="79">
+      <c r="E7" s="72">
         <f t="shared" si="0"/>
-        <v>1743.75</v>
-      </c>
-      <c r="F7" s="79">
+        <v>1656.57</v>
+      </c>
+      <c r="F7" s="72">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G7" s="79">
+      <c r="G7" s="72">
         <f t="shared" si="7"/>
-        <v>-1743.75</v>
-      </c>
-      <c r="H7" s="79">
+        <v>-1569.3899999999999</v>
+      </c>
+      <c r="H7" s="72">
         <f t="shared" si="2"/>
-        <v>1743.75</v>
-      </c>
-      <c r="I7" s="77">
+        <v>1656.57</v>
+      </c>
+      <c r="I7" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="77">
+        <v>4.9995698924731186E-2</v>
+      </c>
+      <c r="J7" s="70">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K7" s="79">
+      <c r="K7" s="72">
         <f t="shared" si="5"/>
-        <v>1743.75</v>
-      </c>
-      <c r="L7" s="81" t="s">
+        <v>1656.57</v>
+      </c>
+      <c r="L7" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="71" t="s">
         <v>340</v>
       </c>
-      <c r="B8" s="79">
+      <c r="B8" s="72">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>8484.7900000000009</v>
       </c>
-      <c r="C8" s="80">
+      <c r="C8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
-      <c r="D8" s="79">
+      <c r="D8" s="72">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5094</v>
       </c>
-      <c r="E8" s="79">
+      <c r="E8" s="72">
         <f t="shared" si="0"/>
         <v>5094</v>
       </c>
-      <c r="F8" s="79">
+      <c r="F8" s="72">
         <f t="shared" si="6"/>
         <v>3390.7900000000009</v>
       </c>
-      <c r="G8" s="79">
+      <c r="G8" s="72">
         <f t="shared" si="7"/>
         <v>-5094</v>
       </c>
-      <c r="H8" s="79">
+      <c r="H8" s="72">
         <f t="shared" si="2"/>
         <v>5094</v>
       </c>
-      <c r="I8" s="77">
+      <c r="I8" s="70">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="70">
         <f t="shared" si="4"/>
         <v>0.60036842396806511</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="72">
         <f t="shared" si="5"/>
         <v>8484.7900000000009</v>
       </c>
-      <c r="L8" s="81" t="s">
+      <c r="L8" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="71" t="s">
         <v>341</v>
       </c>
-      <c r="B9" s="82">
+      <c r="B9" s="74">
         <f>SUM(B2:B8)</f>
         <v>66043.360000000001</v>
       </c>
-      <c r="C9" s="82">
+      <c r="C9" s="74">
         <f>SUM(C2:C8)</f>
-        <v>31721.969999999994</v>
-      </c>
-      <c r="D9" s="82">
+        <v>32316.599999999995</v>
+      </c>
+      <c r="D9" s="74">
         <f>SUM(D2:D8)</f>
         <v>58094.57</v>
       </c>
-      <c r="E9" s="79">
+      <c r="E9" s="72">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>26372.600000000006</v>
-      </c>
-      <c r="F9" s="79">
+        <v>25777.970000000005</v>
+      </c>
+      <c r="F9" s="72">
         <f t="shared" ref="F9" si="9">B9-D9</f>
         <v>7948.7900000000009</v>
       </c>
-      <c r="G9" s="79">
+      <c r="G9" s="72">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>5349.3699999999881</v>
-      </c>
-      <c r="H9" s="79">
+        <v>6538.6299999999901</v>
+      </c>
+      <c r="H9" s="72">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>26372.600000000006</v>
-      </c>
-      <c r="I9" s="77">
+        <v>25777.970000000005</v>
+      </c>
+      <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.48032035317403587</v>
-      </c>
-      <c r="J9" s="77">
+        <v>0.48932398351628376</v>
+      </c>
+      <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
         <v>0.87964285887332205</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="72">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>34321.390000000007</v>
-      </c>
-      <c r="L9" s="81" t="s">
+        <v>33726.760000000009</v>
+      </c>
+      <c r="L9" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6366,128 +6362,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="70" t="s">
+      <c r="A4" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="76"/>
+      <c r="C4" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="71"/>
-      <c r="E4" s="70" t="s">
+      <c r="D4" s="76"/>
+      <c r="E4" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="71"/>
-      <c r="G4" s="70" t="s">
+      <c r="F4" s="76"/>
+      <c r="G4" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="71"/>
+      <c r="H4" s="76"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="72">
+      <c r="A5" s="77">
         <f>Presupuesto!E11</f>
         <v>43821.59</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="72">
+      <c r="B5" s="76"/>
+      <c r="C5" s="77">
         <f>Compras_Materiales!L120+Pago_Obreros!M47</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D5" s="71"/>
-      <c r="E5" s="72">
+      <c r="D5" s="76"/>
+      <c r="E5" s="77">
         <f>A5-C5</f>
         <v>22037.563618134853</v>
       </c>
-      <c r="F5" s="71"/>
-      <c r="G5" s="75">
+      <c r="F5" s="76"/>
+      <c r="G5" s="80">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
-      <c r="H5" s="71"/>
+      <c r="H5" s="76"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
+      <c r="A6" s="76"/>
+      <c r="B6" s="76"/>
+      <c r="C6" s="76"/>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="70" t="s">
+      <c r="B7" s="76"/>
+      <c r="C7" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="71"/>
-      <c r="E7" s="70" t="s">
+      <c r="D7" s="76"/>
+      <c r="E7" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="71"/>
-      <c r="G7" s="70" t="s">
+      <c r="F7" s="76"/>
+      <c r="G7" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="71"/>
+      <c r="H7" s="76"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="72">
+      <c r="A8" s="77">
         <f>B23</f>
         <v>33203.99</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="72">
+      <c r="B8" s="76"/>
+      <c r="C8" s="77">
         <f>C14</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="72">
+      <c r="D8" s="76"/>
+      <c r="E8" s="77">
         <f>A8-C8</f>
         <v>11419.963618134854</v>
       </c>
-      <c r="F8" s="71"/>
-      <c r="G8" s="75">
+      <c r="F8" s="76"/>
+      <c r="G8" s="80">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
-      <c r="H8" s="71"/>
+      <c r="H8" s="76"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="71"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -6743,20 +6739,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6898,32 +6894,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11371,38 +11367,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D356644D-56A4-400B-A8B1-6A6FE3D380E0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6E0035-01B7-474D-ACFE-0B3BD06D33E2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1216,7 +1216,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1319,15 +1319,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1335,7 +1326,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1515,18 +1506,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1534,12 +1513,25 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1549,6 +1541,422 @@
     <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="54">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2640,422 +3048,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF1E293B"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5518,96 +5510,96 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="A1:L9" xr:uid="{A4D9C4A4-4BEE-43F7-B482-6B69DD695700}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="47">
+    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="3">
       <calculatedColumnFormula>D2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="46">
+    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="2">
       <calculatedColumnFormula>B2-D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="45">
+    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="1">
       <calculatedColumnFormula>C2-E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="44">
+    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="11">
       <calculatedColumnFormula>E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="43" dataCellStyle="Porcentaje">
+    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="10" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="42" dataCellStyle="Porcentaje">
+    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="9" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>D2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="41">
+    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="0">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A4:E10" xr:uid="{8ABC211C-7D80-490C-9B76-89253396DB9F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
   <autoFilter ref="A4:M119" xr:uid="{C3432B77-315D-40F3-A17B-615A4A292D9C}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="21" dataCellStyle="Millares">
+    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="39"/>
+    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="35" dataCellStyle="Millares">
       <calculatedColumnFormula>Tabla4[[#This Row],[Cantidad]]*Tabla4[[#This Row],[Precio Unitario Bs]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
   <autoFilter ref="A4:N46" xr:uid="{EA34636B-E6DC-4743-A5C0-1FA27FABC114}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="8" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="7" dataCellStyle="Millares"/>
-    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="5" dataCellStyle="Millares"/>
-    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5911,77 +5903,77 @@
     <col min="8" max="8" width="12.28515625" style="32" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" style="32" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" style="69" customWidth="1"/>
-    <col min="11" max="11" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="77" t="s">
         <v>333</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="77" t="s">
         <v>327</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="77" t="s">
         <v>342</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="77" t="s">
         <v>343</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="77" t="s">
         <v>344</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="77" t="s">
         <v>328</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="77" t="s">
         <v>329</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="77" t="s">
         <v>348</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="77" t="s">
         <v>330</v>
       </c>
       <c r="J1" s="70" t="s">
         <v>331</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="77" t="s">
         <v>332</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="77" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="78" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="72">
+      <c r="B2" s="81">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>38605.82</v>
       </c>
-      <c r="C2" s="73">
+      <c r="C2" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>28086.599999999995</v>
       </c>
-      <c r="D2" s="72">
+      <c r="D2" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>38605.82</v>
       </c>
-      <c r="E2" s="72">
+      <c r="E2" s="81">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
         <v>10519.220000000005</v>
       </c>
-      <c r="F2" s="72">
+      <c r="F2" s="81">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="72">
+      <c r="G2" s="81">
         <f t="shared" si="1"/>
         <v>17567.37999999999</v>
       </c>
-      <c r="H2" s="72">
+      <c r="H2" s="79">
         <f t="shared" ref="H2:H8" si="2">E2</f>
         <v>10519.220000000005</v>
       </c>
@@ -5993,43 +5985,43 @@
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
         <v>1</v>
       </c>
-      <c r="K2" s="72">
+      <c r="K2" s="81">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
         <v>10519.220000000005</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="80" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="78" t="s">
         <v>335</v>
       </c>
-      <c r="B3" s="72">
+      <c r="B3" s="81">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C3" s="73">
+      <c r="C3" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D3" s="72">
+      <c r="D3" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E3" s="72">
+      <c r="E3" s="81">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F3" s="72">
+      <c r="F3" s="81">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G3" s="72">
+      <c r="G3" s="81">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H3" s="72">
+      <c r="H3" s="79">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -6041,43 +6033,43 @@
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K3" s="72">
+      <c r="K3" s="81">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="80" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="78" t="s">
         <v>336</v>
       </c>
-      <c r="B4" s="72">
+      <c r="B4" s="81">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C4" s="73">
+      <c r="C4" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D4" s="72">
+      <c r="D4" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="81">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F4" s="72">
+      <c r="F4" s="81">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G4" s="72">
+      <c r="G4" s="81">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H4" s="72">
+      <c r="H4" s="79">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -6089,43 +6081,43 @@
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K4" s="72">
+      <c r="K4" s="81">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="80" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="78" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="72">
+      <c r="B5" s="81">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>10524</v>
       </c>
-      <c r="C5" s="73">
+      <c r="C5" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>3236.5699999999997</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>6314</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="81">
         <f t="shared" si="0"/>
         <v>3077.4300000000003</v>
       </c>
-      <c r="F5" s="72">
+      <c r="F5" s="81">
         <f t="shared" ref="F5:F8" si="6">B5-D5</f>
         <v>4210</v>
       </c>
-      <c r="G5" s="72">
+      <c r="G5" s="81">
         <f t="shared" ref="G5:G8" si="7">C5-E5</f>
         <v>159.13999999999942</v>
       </c>
-      <c r="H5" s="72">
+      <c r="H5" s="79">
         <f t="shared" si="2"/>
         <v>3077.4300000000003</v>
       </c>
@@ -6137,43 +6129,43 @@
         <f t="shared" si="4"/>
         <v>0.59996199163816044</v>
       </c>
-      <c r="K5" s="72">
+      <c r="K5" s="81">
         <f t="shared" si="5"/>
         <v>7287.43</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="80" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="78" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="72">
+      <c r="B6" s="81">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>5525</v>
       </c>
-      <c r="C6" s="73">
+      <c r="C6" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>276.25</v>
       </c>
-      <c r="D6" s="72">
+      <c r="D6" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5525</v>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="81">
         <f t="shared" si="0"/>
         <v>5248.75</v>
       </c>
-      <c r="F6" s="72">
+      <c r="F6" s="81">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G6" s="72">
+      <c r="G6" s="81">
         <f t="shared" si="7"/>
         <v>-4972.5</v>
       </c>
-      <c r="H6" s="72">
+      <c r="H6" s="79">
         <f t="shared" si="2"/>
         <v>5248.75</v>
       </c>
@@ -6185,43 +6177,43 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K6" s="72">
+      <c r="K6" s="81">
         <f t="shared" si="5"/>
         <v>5248.75</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="80" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="78" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="72">
+      <c r="B7" s="81">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>1743.75</v>
       </c>
-      <c r="C7" s="73">
+      <c r="C7" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>87.18</v>
       </c>
-      <c r="D7" s="72">
+      <c r="D7" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>1743.75</v>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="81">
         <f t="shared" si="0"/>
         <v>1656.57</v>
       </c>
-      <c r="F7" s="72">
+      <c r="F7" s="81">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G7" s="72">
+      <c r="G7" s="81">
         <f t="shared" si="7"/>
         <v>-1569.3899999999999</v>
       </c>
-      <c r="H7" s="72">
+      <c r="H7" s="79">
         <f t="shared" si="2"/>
         <v>1656.57</v>
       </c>
@@ -6233,107 +6225,107 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="81">
         <f t="shared" si="5"/>
         <v>1656.57</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="80" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="78" t="s">
         <v>340</v>
       </c>
-      <c r="B8" s="72">
+      <c r="B8" s="81">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>8484.7900000000009</v>
       </c>
-      <c r="C8" s="73">
+      <c r="C8" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="72">
+        <v>2638.15</v>
+      </c>
+      <c r="D8" s="81">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5094</v>
       </c>
-      <c r="E8" s="72">
+      <c r="E8" s="81">
         <f t="shared" si="0"/>
-        <v>5094</v>
-      </c>
-      <c r="F8" s="72">
+        <v>2455.85</v>
+      </c>
+      <c r="F8" s="81">
         <f t="shared" si="6"/>
         <v>3390.7900000000009</v>
       </c>
-      <c r="G8" s="72">
+      <c r="G8" s="81">
         <f t="shared" si="7"/>
-        <v>-5094</v>
-      </c>
-      <c r="H8" s="72">
+        <v>182.30000000000018</v>
+      </c>
+      <c r="H8" s="79">
         <f t="shared" si="2"/>
-        <v>5094</v>
+        <v>2455.85</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.31092696460372027</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="4"/>
         <v>0.60036842396806511</v>
       </c>
-      <c r="K8" s="72">
+      <c r="K8" s="81">
         <f t="shared" si="5"/>
-        <v>8484.7900000000009</v>
-      </c>
-      <c r="L8" t="s">
+        <v>5846.6400000000012</v>
+      </c>
+      <c r="L8" s="80" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="78" t="s">
         <v>341</v>
       </c>
-      <c r="B9" s="74">
+      <c r="B9" s="81">
         <f>SUM(B2:B8)</f>
         <v>66043.360000000001</v>
       </c>
-      <c r="C9" s="74">
+      <c r="C9" s="81">
         <f>SUM(C2:C8)</f>
-        <v>32316.599999999995</v>
-      </c>
-      <c r="D9" s="74">
+        <v>34954.749999999993</v>
+      </c>
+      <c r="D9" s="81">
         <f>SUM(D2:D8)</f>
         <v>58094.57</v>
       </c>
-      <c r="E9" s="72">
+      <c r="E9" s="81">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>25777.970000000005</v>
-      </c>
-      <c r="F9" s="72">
+        <v>23139.820000000007</v>
+      </c>
+      <c r="F9" s="81">
         <f t="shared" ref="F9" si="9">B9-D9</f>
         <v>7948.7900000000009</v>
       </c>
-      <c r="G9" s="72">
+      <c r="G9" s="81">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>6538.6299999999901</v>
-      </c>
-      <c r="H9" s="72">
+        <v>11814.929999999986</v>
+      </c>
+      <c r="H9" s="79">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>25777.970000000005</v>
+        <v>23139.820000000007</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.48932398351628376</v>
+        <v>0.52926971008137669</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
         <v>0.87964285887332205</v>
       </c>
-      <c r="K9" s="72">
+      <c r="K9" s="81">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>33726.760000000009</v>
-      </c>
-      <c r="L9" t="s">
+        <v>31088.610000000008</v>
+      </c>
+      <c r="L9" s="80" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6362,128 +6354,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="76"/>
-      <c r="C4" s="75" t="s">
+      <c r="A4" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="76"/>
-      <c r="E4" s="75" t="s">
+      <c r="D4" s="72"/>
+      <c r="E4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="76"/>
-      <c r="G4" s="75" t="s">
+      <c r="F4" s="72"/>
+      <c r="G4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="76"/>
+      <c r="H4" s="72"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="77">
+      <c r="A5" s="73">
         <f>Presupuesto!E11</f>
         <v>43821.59</v>
       </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="77">
+      <c r="B5" s="72"/>
+      <c r="C5" s="73">
         <f>Compras_Materiales!L120+Pago_Obreros!M47</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D5" s="76"/>
-      <c r="E5" s="77">
+      <c r="D5" s="72"/>
+      <c r="E5" s="73">
         <f>A5-C5</f>
         <v>22037.563618134853</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="80">
+      <c r="F5" s="72"/>
+      <c r="G5" s="74">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
-      <c r="H5" s="76"/>
+      <c r="H5" s="72"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
-      <c r="E6" s="76"/>
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="75" t="s">
+      <c r="B7" s="72"/>
+      <c r="C7" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="76"/>
-      <c r="E7" s="75" t="s">
+      <c r="D7" s="72"/>
+      <c r="E7" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="76"/>
-      <c r="G7" s="75" t="s">
+      <c r="F7" s="72"/>
+      <c r="G7" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="76"/>
+      <c r="H7" s="72"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="77">
+      <c r="A8" s="73">
         <f>B23</f>
         <v>33203.99</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="77">
+      <c r="B8" s="72"/>
+      <c r="C8" s="73">
         <f>C14</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D8" s="76"/>
-      <c r="E8" s="77">
+      <c r="D8" s="72"/>
+      <c r="E8" s="73">
         <f>A8-C8</f>
         <v>11419.963618134854</v>
       </c>
-      <c r="F8" s="76"/>
-      <c r="G8" s="80">
+      <c r="F8" s="72"/>
+      <c r="G8" s="74">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
-      <c r="H8" s="76"/>
+      <c r="H8" s="72"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="76"/>
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -6703,14 +6695,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6720,6 +6704,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6739,20 +6731,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6894,32 +6886,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11367,38 +11359,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6E0035-01B7-474D-ACFE-0B3BD06D33E2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6A23CA-FD30-46B4-9025-43A6A9010F34}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1326,7 +1326,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1506,6 +1506,15 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1513,25 +1522,12 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1541,422 +1537,6 @@
     <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="54">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFCBD5E1"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFCBD5E1"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFCBD5E1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF1E293B"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FFCBD5E1"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -3048,6 +2628,422 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1E293B"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFCBD5E1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD5E1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD5E1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD5E1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -5510,96 +5506,96 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C5805E51-A356-4DF4-A8E3-9FB386CF607D}" name="Tabla1" displayName="Tabla1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
   <autoFilter ref="A1:L9" xr:uid="{A4D9C4A4-4BEE-43F7-B482-6B69DD695700}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{9639892B-B05F-4273-A2D0-0F26C4BDA78B}" name="Obra" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{E24FABEC-6585-475F-BD45-D7E037225687}" name="Monto Contrato" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{59352CEA-A0C7-4891-8730-9739502D15D6}" name="EJECUTADO" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{4D528DAA-1E81-4553-8223-9B69EF0E3B7B}" name="DESEMBOLSADO" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{18FC4046-0DCE-4C45-8BF6-56269B2E56F6}" name="FLUJO DE CAJA" dataDxfId="47">
       <calculatedColumnFormula>D2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="2">
+    <tableColumn id="6" xr3:uid="{899F9DB9-CF23-4328-AFEE-25EC12A8B325}" name="Por cobrar" dataDxfId="46">
       <calculatedColumnFormula>B2-D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="1">
+    <tableColumn id="7" xr3:uid="{B77ECBA9-3527-4393-B393-7789EFC2DE7E}" name="Utilidad Bruta" dataDxfId="45">
       <calculatedColumnFormula>C2-E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="11">
+    <tableColumn id="8" xr3:uid="{D9267B23-8841-4BA0-9258-A82B5D1E3C15}" name="Flujo de Caja2" dataDxfId="44">
       <calculatedColumnFormula>E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="10" dataCellStyle="Porcentaje">
+    <tableColumn id="9" xr3:uid="{5216BE03-89CB-4506-AD80-2A2BC0249463}" name="% Avance Facturado" dataDxfId="43" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>C2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="9" dataCellStyle="Porcentaje">
+    <tableColumn id="10" xr3:uid="{B3979176-8352-4A1E-8E53-38F1851C0B62}" name="% Avance Cobrado" dataDxfId="42" dataCellStyle="Porcentaje">
       <calculatedColumnFormula>D2/B2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{94A9DD3A-AA85-4291-8F0F-8D0CF97A777A}" name="Saldo por Ejecutar" dataDxfId="41">
       <calculatedColumnFormula>B2-C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{7A3B3339-89C3-4CDF-9786-F758C4867EFC}" name="Estado" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="53" dataDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A4:E10" xr:uid="{8ABC211C-7D80-490C-9B76-89253396DB9F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{84E4A345-4F70-4242-AEBF-DEFE862C7201}" name="Item" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{2764A18A-9183-4772-8CF7-B73D203823AA}" name="Descripción de Partida" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{862DB45F-14BD-479A-A469-1805C47768C4}" name="Unidad" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{3D7A14B7-3496-46E7-91C0-3D3429704BE1}" name="Cantidad" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{E49A0B03-5910-4839-A117-212DE1184427}" name="Costo Total Presupuestado ($)" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" tableBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4BBD0D97-159B-4352-8764-5DB39DBC8043}" name="Tabla4" displayName="Tabla4" ref="A4:M119" insertRowShift="1" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
   <autoFilter ref="A4:M119" xr:uid="{C3432B77-315D-40F3-A17B-615A4A292D9C}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="39"/>
-    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="38"/>
-    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="36" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="35" dataCellStyle="Millares">
+    <tableColumn id="1" xr3:uid="{51E61233-9233-43B7-BB64-29A901BAEA30}" name="ID Compra" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9C29F3DD-7251-4C67-BC5D-7306B08C10A3}" name="Fecha" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{C03286CD-E636-4F93-B5BB-FD2EF9316000}" name="Proveedor" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{C3E7CDCA-7AC6-4AF8-A142-431E93F82507}" name="N° Factura" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{1C36C9FC-DD95-4DD5-BF63-11F86DA703F7}" name="Descripción del Material" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{BF187DCE-C330-4566-80EA-1C65219FCD24}" name="Proyecto" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{07AC7C56-D870-42C9-A2B1-62222E777EAC}" name="Cantidad" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{37E43724-D57F-4009-AFAE-310807BA6141}" name="Precio Unitario Bs" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{20E3667F-97A8-40CB-9D83-5580EEF43828}" name="Precio Total Bs" dataDxfId="21" dataCellStyle="Millares">
       <calculatedColumnFormula>Tabla4[[#This Row],[Cantidad]]*Tabla4[[#This Row],[Precio Unitario Bs]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="31"/>
+    <tableColumn id="12" xr3:uid="{4F7720D4-B9D1-4D0E-B98C-1D2DF82D3219}" name="Tasa" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{121DB662-44AD-4135-8A9A-13D6E424C364}" name="Precio Unitario ($)" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{C8E4D933-4F1F-49BC-8EE3-2244B02AB1BB}" name="Precio Total ($)" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{91480AE5-00CF-4555-9CD6-E1FBDFDC6A12}" name="Estado / Observación" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C237523-723C-417F-A723-6C941585734B}" name="Tabla5" displayName="Tabla5" ref="A4:N46" insertRowShift="1" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A4:N46" xr:uid="{EA34636B-E6DC-4743-A5C0-1FA27FABC114}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{BBAF9CF5-2C57-497C-ADCC-BC3BCE11CE82}" name="N° Sem" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{60AD9872-1C78-49BE-BE30-236230C9FAFB}" name="Inicio labor" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{B6A1A3AE-C552-4972-B3CF-C312F8E83741}" name="Fecha Pago" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{403A8C63-508B-46D2-AF7D-E343A87090BC}" name="Nombre del Trabajador" dataDxfId="10"/>
+    <tableColumn id="11" xr3:uid="{E332BA78-D135-4112-89B9-EE8E17A08EDA}" name="CI" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{926F1834-F424-44C6-815B-F614EC784ECB}" name="N° Cuenta" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{21A18727-7773-4BC6-9C1B-288F81640406}" name="Banco" dataDxfId="7" dataCellStyle="Millares"/>
+    <tableColumn id="4" xr3:uid="{97A20550-620F-4113-9F6C-9583687D28BA}" name="Cargo / Rol" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{C4861E6E-432A-479E-B56C-C8DDC5439D01}" name="Días Trabajados" dataDxfId="5" dataCellStyle="Millares"/>
+    <tableColumn id="6" xr3:uid="{D8A42229-F2C3-45EB-AA32-B6A5645D3970}" name="Pago Diario ($)" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{ECD689E9-2C20-47A1-AAE6-3C4B456C6E73}" name="Bonificación ($)" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B708F2B1-6B11-4DD2-BD9A-DFF48B584291}" name="Deducciones ($)" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{CF88BABA-BA05-4A83-A637-4B472029040F}" name="Total Pagado ($)" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{8B29990E-C3AB-45EA-9AE7-197947CFEB49}" name="Notas / Frente de Trabajo" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5908,72 +5904,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="32" t="s">
         <v>333</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="32" t="s">
         <v>327</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="32" t="s">
         <v>342</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="E1" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="F1" s="77" t="s">
+      <c r="F1" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="H1" s="77" t="s">
+      <c r="H1" s="32" t="s">
         <v>348</v>
       </c>
-      <c r="I1" s="77" t="s">
+      <c r="I1" s="32" t="s">
         <v>330</v>
       </c>
       <c r="J1" s="70" t="s">
         <v>331</v>
       </c>
-      <c r="K1" s="77" t="s">
+      <c r="K1" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="L1" s="77" t="s">
+      <c r="L1" s="32" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="71" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="81">
+      <c r="B2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>38605.82</v>
       </c>
-      <c r="C2" s="81">
+      <c r="C2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>28086.599999999995</v>
       </c>
-      <c r="D2" s="81">
+      <c r="D2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>38605.82</v>
       </c>
-      <c r="E2" s="81">
+      <c r="E2" s="73">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
         <v>10519.220000000005</v>
       </c>
-      <c r="F2" s="81">
+      <c r="F2" s="73">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="81">
+      <c r="G2" s="73">
         <f t="shared" si="1"/>
         <v>17567.37999999999</v>
       </c>
-      <c r="H2" s="79">
+      <c r="H2" s="72">
         <f t="shared" ref="H2:H8" si="2">E2</f>
         <v>10519.220000000005</v>
       </c>
@@ -5985,43 +5981,43 @@
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
         <v>1</v>
       </c>
-      <c r="K2" s="81">
+      <c r="K2" s="73">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
         <v>10519.220000000005</v>
       </c>
-      <c r="L2" s="80" t="s">
+      <c r="L2" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="71" t="s">
         <v>335</v>
       </c>
-      <c r="B3" s="81">
+      <c r="B3" s="73">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C3" s="81">
+      <c r="C3" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D3" s="81">
+      <c r="D3" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E3" s="81">
+      <c r="E3" s="73">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F3" s="81">
+      <c r="F3" s="73">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G3" s="81">
+      <c r="G3" s="73">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H3" s="79">
+      <c r="H3" s="72">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -6033,43 +6029,43 @@
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K3" s="81">
+      <c r="K3" s="73">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L3" s="80" t="s">
+      <c r="L3" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="71" t="s">
         <v>336</v>
       </c>
-      <c r="B4" s="81">
+      <c r="B4" s="73">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
-      <c r="D4" s="81">
+      <c r="D4" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="73">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="F4" s="81">
+      <c r="F4" s="73">
         <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="G4" s="81">
+      <c r="G4" s="73">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="H4" s="79">
+      <c r="H4" s="72">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -6081,43 +6077,43 @@
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="K4" s="81">
+      <c r="K4" s="73">
         <f t="shared" si="5"/>
         <v>265</v>
       </c>
-      <c r="L4" s="80" t="s">
+      <c r="L4" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="71" t="s">
         <v>337</v>
       </c>
-      <c r="B5" s="81">
+      <c r="B5" s="73">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>10524</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>3236.5699999999997</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>6314</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="73">
         <f t="shared" si="0"/>
         <v>3077.4300000000003</v>
       </c>
-      <c r="F5" s="81">
+      <c r="F5" s="73">
         <f t="shared" ref="F5:F8" si="6">B5-D5</f>
         <v>4210</v>
       </c>
-      <c r="G5" s="81">
+      <c r="G5" s="73">
         <f t="shared" ref="G5:G8" si="7">C5-E5</f>
         <v>159.13999999999942</v>
       </c>
-      <c r="H5" s="79">
+      <c r="H5" s="72">
         <f t="shared" si="2"/>
         <v>3077.4300000000003</v>
       </c>
@@ -6129,43 +6125,43 @@
         <f t="shared" si="4"/>
         <v>0.59996199163816044</v>
       </c>
-      <c r="K5" s="81">
+      <c r="K5" s="73">
         <f t="shared" si="5"/>
         <v>7287.43</v>
       </c>
-      <c r="L5" s="80" t="s">
+      <c r="L5" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="71" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="81">
+      <c r="B6" s="73">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>5525</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>276.25</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5525</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="73">
         <f t="shared" si="0"/>
         <v>5248.75</v>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="73">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="73">
         <f t="shared" si="7"/>
         <v>-4972.5</v>
       </c>
-      <c r="H6" s="79">
+      <c r="H6" s="72">
         <f t="shared" si="2"/>
         <v>5248.75</v>
       </c>
@@ -6177,43 +6173,43 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K6" s="81">
+      <c r="K6" s="73">
         <f t="shared" si="5"/>
         <v>5248.75</v>
       </c>
-      <c r="L6" s="80" t="s">
+      <c r="L6" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="71" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="81">
+      <c r="B7" s="73">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>1743.75</v>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>87.18</v>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>1743.75</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="73">
         <f t="shared" si="0"/>
         <v>1656.57</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="73">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="73">
         <f t="shared" si="7"/>
         <v>-1569.3899999999999</v>
       </c>
-      <c r="H7" s="79">
+      <c r="H7" s="72">
         <f t="shared" si="2"/>
         <v>1656.57</v>
       </c>
@@ -6225,107 +6221,107 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="K7" s="81">
+      <c r="K7" s="73">
         <f t="shared" si="5"/>
         <v>1656.57</v>
       </c>
-      <c r="L7" s="80" t="s">
+      <c r="L7" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="71" t="s">
         <v>340</v>
       </c>
-      <c r="B8" s="81">
+      <c r="B8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>8484.7900000000009</v>
       </c>
-      <c r="C8" s="81">
+      <c r="C8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>2638.15</v>
-      </c>
-      <c r="D8" s="81">
+        <v>2684.4700000000003</v>
+      </c>
+      <c r="D8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5094</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="73">
         <f t="shared" si="0"/>
-        <v>2455.85</v>
-      </c>
-      <c r="F8" s="81">
+        <v>2409.5299999999997</v>
+      </c>
+      <c r="F8" s="73">
         <f t="shared" si="6"/>
         <v>3390.7900000000009</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="73">
         <f t="shared" si="7"/>
-        <v>182.30000000000018</v>
-      </c>
-      <c r="H8" s="79">
+        <v>274.94000000000051</v>
+      </c>
+      <c r="H8" s="72">
         <f t="shared" si="2"/>
-        <v>2455.85</v>
+        <v>2409.5299999999997</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="3"/>
-        <v>0.31092696460372027</v>
+        <v>0.31638614509021434</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="4"/>
         <v>0.60036842396806511</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="73">
         <f t="shared" si="5"/>
-        <v>5846.6400000000012</v>
-      </c>
-      <c r="L8" s="80" t="s">
+        <v>5800.3200000000006</v>
+      </c>
+      <c r="L8" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="71" t="s">
         <v>341</v>
       </c>
-      <c r="B9" s="81">
+      <c r="B9" s="73">
         <f>SUM(B2:B8)</f>
         <v>66043.360000000001</v>
       </c>
-      <c r="C9" s="81">
+      <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>34954.749999999993</v>
-      </c>
-      <c r="D9" s="81">
+        <v>35001.069999999992</v>
+      </c>
+      <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
         <v>58094.57</v>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="73">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>23139.820000000007</v>
-      </c>
-      <c r="F9" s="81">
+        <v>23093.500000000007</v>
+      </c>
+      <c r="F9" s="73">
         <f t="shared" ref="F9" si="9">B9-D9</f>
         <v>7948.7900000000009</v>
       </c>
-      <c r="G9" s="81">
+      <c r="G9" s="73">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>11814.929999999986</v>
-      </c>
-      <c r="H9" s="79">
+        <v>11907.569999999985</v>
+      </c>
+      <c r="H9" s="72">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>23139.820000000007</v>
+        <v>23093.500000000007</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.52926971008137669</v>
+        <v>0.52997106749262901</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
         <v>0.87964285887332205</v>
       </c>
-      <c r="K9" s="81">
+      <c r="K9" s="73">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>31088.610000000008</v>
-      </c>
-      <c r="L9" s="80" t="s">
+        <v>31042.290000000008</v>
+      </c>
+      <c r="L9" t="s">
         <v>347</v>
       </c>
     </row>
@@ -6354,128 +6350,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="71" t="s">
+      <c r="A4" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="75"/>
+      <c r="C4" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="71" t="s">
+      <c r="D4" s="75"/>
+      <c r="E4" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="72"/>
-      <c r="G4" s="71" t="s">
+      <c r="F4" s="75"/>
+      <c r="G4" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="72"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="73">
+      <c r="A5" s="76">
         <f>Presupuesto!E11</f>
         <v>43821.59</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73">
+      <c r="B5" s="75"/>
+      <c r="C5" s="76">
         <f>Compras_Materiales!L120+Pago_Obreros!M47</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D5" s="72"/>
-      <c r="E5" s="73">
+      <c r="D5" s="75"/>
+      <c r="E5" s="76">
         <f>A5-C5</f>
         <v>22037.563618134853</v>
       </c>
-      <c r="F5" s="72"/>
-      <c r="G5" s="74">
+      <c r="F5" s="75"/>
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
-      <c r="H5" s="72"/>
+      <c r="H5" s="75"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="71" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="71" t="s">
+      <c r="D7" s="75"/>
+      <c r="E7" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="72"/>
-      <c r="G7" s="71" t="s">
+      <c r="F7" s="75"/>
+      <c r="G7" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="72"/>
+      <c r="H7" s="75"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="73">
+      <c r="A8" s="76">
         <f>B23</f>
         <v>33203.99</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="73">
+      <c r="B8" s="75"/>
+      <c r="C8" s="76">
         <f>C14</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="73">
+      <c r="D8" s="75"/>
+      <c r="E8" s="76">
         <f>A8-C8</f>
         <v>11419.963618134854</v>
       </c>
-      <c r="F8" s="72"/>
-      <c r="G8" s="74">
+      <c r="F8" s="75"/>
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
-      <c r="H8" s="72"/>
+      <c r="H8" s="75"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -6695,6 +6691,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6704,14 +6708,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6731,20 +6727,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6886,32 +6882,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11359,38 +11355,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="76"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6A23CA-FD30-46B4-9025-43A6A9010F34}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2B5CB9-9A14-4570-A41D-7877731D3691}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>28086.599999999995</v>
+        <v>28116.849999999995</v>
       </c>
       <c r="D2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="E2" s="73">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>10519.220000000005</v>
+        <v>10488.970000000005</v>
       </c>
       <c r="F2" s="73">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5967,15 +5967,15 @@
       </c>
       <c r="G2" s="73">
         <f t="shared" si="1"/>
-        <v>17567.37999999999</v>
+        <v>17627.87999999999</v>
       </c>
       <c r="H2" s="72">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>10519.220000000005</v>
+        <v>10488.970000000005</v>
       </c>
       <c r="I2" s="70">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.72752243055580723</v>
+        <v>0.72830599116920702</v>
       </c>
       <c r="J2" s="70">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="K2" s="73">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>10519.220000000005</v>
+        <v>10488.970000000005</v>
       </c>
       <c r="L2" t="s">
         <v>346</v>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="C8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>2684.4700000000003</v>
+        <v>3207.19</v>
       </c>
       <c r="D8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="E8" s="73">
         <f t="shared" si="0"/>
-        <v>2409.5299999999997</v>
+        <v>1886.81</v>
       </c>
       <c r="F8" s="73">
         <f t="shared" si="6"/>
@@ -6255,15 +6255,15 @@
       </c>
       <c r="G8" s="73">
         <f t="shared" si="7"/>
-        <v>274.94000000000051</v>
+        <v>1320.38</v>
       </c>
       <c r="H8" s="72">
         <f t="shared" si="2"/>
-        <v>2409.5299999999997</v>
+        <v>1886.81</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="3"/>
-        <v>0.31638614509021434</v>
+        <v>0.37799285545075362</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="4"/>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="K8" s="73">
         <f t="shared" si="5"/>
-        <v>5800.3200000000006</v>
+        <v>5277.6</v>
       </c>
       <c r="L8" t="s">
         <v>347</v>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>35001.069999999992</v>
+        <v>35554.039999999994</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="E9" s="73">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>23093.500000000007</v>
+        <v>22540.530000000006</v>
       </c>
       <c r="F9" s="73">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -6303,15 +6303,15 @@
       </c>
       <c r="G9" s="73">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>11907.569999999985</v>
+        <v>13013.509999999987</v>
       </c>
       <c r="H9" s="72">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>23093.500000000007</v>
+        <v>22540.530000000006</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.52997106749262901</v>
+        <v>0.53834390012864264</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>31042.290000000008</v>
+        <v>30489.320000000007</v>
       </c>
       <c r="L9" t="s">
         <v>347</v>
@@ -6350,28 +6350,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -6407,7 +6407,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6691,14 +6691,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6708,6 +6700,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6727,20 +6727,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6882,32 +6882,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11355,38 +11355,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2B5CB9-9A14-4570-A41D-7877731D3691}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCE60F3-A99C-4ABA-BA39-F55FBF7D1BB1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5494,12 +5494,14 @@
     <sheetNames>
       <sheetName val="Panel_de_Control"/>
       <sheetName val="Registro_Transacciones"/>
+      <sheetName val="Por pagar"/>
       <sheetName val="Configuracion"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6239,7 +6241,7 @@
       </c>
       <c r="C8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>3207.19</v>
+        <v>4317.76</v>
       </c>
       <c r="D8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -6247,7 +6249,7 @@
       </c>
       <c r="E8" s="73">
         <f t="shared" si="0"/>
-        <v>1886.81</v>
+        <v>776.23999999999978</v>
       </c>
       <c r="F8" s="73">
         <f t="shared" si="6"/>
@@ -6255,15 +6257,15 @@
       </c>
       <c r="G8" s="73">
         <f t="shared" si="7"/>
-        <v>1320.38</v>
+        <v>3541.5200000000004</v>
       </c>
       <c r="H8" s="72">
         <f t="shared" si="2"/>
-        <v>1886.81</v>
+        <v>776.23999999999978</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="3"/>
-        <v>0.37799285545075362</v>
+        <v>0.50888236479630022</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="4"/>
@@ -6271,7 +6273,7 @@
       </c>
       <c r="K8" s="73">
         <f t="shared" si="5"/>
-        <v>5277.6</v>
+        <v>4167.0300000000007</v>
       </c>
       <c r="L8" t="s">
         <v>347</v>
@@ -6287,7 +6289,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>35554.039999999994</v>
+        <v>36664.609999999993</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -6295,7 +6297,7 @@
       </c>
       <c r="E9" s="73">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>22540.530000000006</v>
+        <v>21429.960000000006</v>
       </c>
       <c r="F9" s="73">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -6303,15 +6305,15 @@
       </c>
       <c r="G9" s="73">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>13013.509999999987</v>
+        <v>15234.649999999987</v>
       </c>
       <c r="H9" s="72">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>22540.530000000006</v>
+        <v>21429.960000000006</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.53834390012864264</v>
+        <v>0.55515967085866003</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -6319,7 +6321,7 @@
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>30489.320000000007</v>
+        <v>29378.750000000007</v>
       </c>
       <c r="L9" t="s">
         <v>347</v>
@@ -6350,28 +6352,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -6407,7 +6409,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6457,7 +6459,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6691,6 +6693,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6700,14 +6710,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6727,20 +6729,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6882,32 +6884,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11355,38 +11357,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCE60F3-A99C-4ABA-BA39-F55FBF7D1BB1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BDC9B6-6B47-4A27-9FF5-756158565E87}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5499,9 +5499,9 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="C2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>28116.849999999995</v>
+        <v>28642.109999999993</v>
       </c>
       <c r="D2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="E2" s="73">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>10488.970000000005</v>
+        <v>9963.7100000000064</v>
       </c>
       <c r="F2" s="73">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5969,15 +5969,15 @@
       </c>
       <c r="G2" s="73">
         <f t="shared" si="1"/>
-        <v>17627.87999999999</v>
+        <v>18678.399999999987</v>
       </c>
       <c r="H2" s="72">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>10488.970000000005</v>
+        <v>9963.7100000000064</v>
       </c>
       <c r="I2" s="70">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.72830599116920702</v>
+        <v>0.74191171175744985</v>
       </c>
       <c r="J2" s="70">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="K2" s="73">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>10488.970000000005</v>
+        <v>9963.7100000000064</v>
       </c>
       <c r="L2" t="s">
         <v>346</v>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>36664.609999999993</v>
+        <v>37189.869999999995</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="E9" s="73">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>21429.960000000006</v>
+        <v>20904.700000000004</v>
       </c>
       <c r="F9" s="73">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -6305,15 +6305,15 @@
       </c>
       <c r="G9" s="73">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>15234.649999999987</v>
+        <v>16285.169999999991</v>
       </c>
       <c r="H9" s="72">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>21429.960000000006</v>
+        <v>20904.700000000004</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.55515967085866003</v>
+        <v>0.56311293065646562</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>29378.750000000007</v>
+        <v>28853.490000000005</v>
       </c>
       <c r="L9" t="s">
         <v>347</v>
@@ -6352,28 +6352,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -6409,7 +6409,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6693,14 +6693,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6710,6 +6702,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6729,20 +6729,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6884,32 +6884,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11357,38 +11357,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BDC9B6-6B47-4A27-9FF5-756158565E87}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8388807-8C3E-4CAB-ACC0-7E1E148621AE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6630" yWindow="720" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5499,9 +5499,9 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="C2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>28642.109999999993</v>
+        <v>29117.439999999995</v>
       </c>
       <c r="D2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="E2" s="73">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>9963.7100000000064</v>
+        <v>9488.3800000000047</v>
       </c>
       <c r="F2" s="73">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5969,15 +5969,15 @@
       </c>
       <c r="G2" s="73">
         <f t="shared" si="1"/>
-        <v>18678.399999999987</v>
+        <v>19629.05999999999</v>
       </c>
       <c r="H2" s="72">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>9963.7100000000064</v>
+        <v>9488.3800000000047</v>
       </c>
       <c r="I2" s="70">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.74191171175744985</v>
+        <v>0.75422410403405482</v>
       </c>
       <c r="J2" s="70">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="K2" s="73">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>9963.7100000000064</v>
+        <v>9488.3800000000047</v>
       </c>
       <c r="L2" t="s">
         <v>346</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>4317.76</v>
+        <v>4359.5400000000009</v>
       </c>
       <c r="D8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E8" s="73">
         <f t="shared" si="0"/>
-        <v>776.23999999999978</v>
+        <v>734.45999999999913</v>
       </c>
       <c r="F8" s="73">
         <f t="shared" si="6"/>
@@ -6257,15 +6257,15 @@
       </c>
       <c r="G8" s="73">
         <f t="shared" si="7"/>
-        <v>3541.5200000000004</v>
+        <v>3625.0800000000017</v>
       </c>
       <c r="H8" s="72">
         <f t="shared" si="2"/>
-        <v>776.23999999999978</v>
+        <v>734.45999999999913</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="3"/>
-        <v>0.50888236479630022</v>
+        <v>0.51380647016602654</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="4"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="K8" s="73">
         <f t="shared" si="5"/>
-        <v>4167.0300000000007</v>
+        <v>4125.25</v>
       </c>
       <c r="L8" t="s">
         <v>347</v>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>37189.869999999995</v>
+        <v>37706.979999999996</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="E9" s="73">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>20904.700000000004</v>
+        <v>20387.590000000004</v>
       </c>
       <c r="F9" s="73">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -6305,15 +6305,15 @@
       </c>
       <c r="G9" s="73">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>16285.169999999991</v>
+        <v>17319.389999999992</v>
       </c>
       <c r="H9" s="72">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>20904.700000000004</v>
+        <v>20387.590000000004</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.56311293065646562</v>
+        <v>0.57094278667832765</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>28853.490000000005</v>
+        <v>28336.380000000005</v>
       </c>
       <c r="L9" t="s">
         <v>347</v>
@@ -6352,28 +6352,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -6409,7 +6409,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6693,6 +6693,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6702,14 +6710,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6729,20 +6729,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6884,32 +6884,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11357,38 +11357,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8388807-8C3E-4CAB-ACC0-7E1E148621AE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C3C68B-BA8D-4C2D-8700-CC0491634AAE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6630" yWindow="720" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5499,9 +5499,9 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="C2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>29117.439999999995</v>
+        <v>29154.799999999996</v>
       </c>
       <c r="D2" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="E2" s="73">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>9488.3800000000047</v>
+        <v>9451.0200000000041</v>
       </c>
       <c r="F2" s="73">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5969,15 +5969,15 @@
       </c>
       <c r="G2" s="73">
         <f t="shared" si="1"/>
-        <v>19629.05999999999</v>
+        <v>19703.779999999992</v>
       </c>
       <c r="H2" s="72">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>9488.3800000000047</v>
+        <v>9451.0200000000041</v>
       </c>
       <c r="I2" s="70">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.75422410403405482</v>
+        <v>0.75519183377014132</v>
       </c>
       <c r="J2" s="70">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="K2" s="73">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>9488.3800000000047</v>
+        <v>9451.0200000000041</v>
       </c>
       <c r="L2" t="s">
         <v>346</v>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>4359.5400000000009</v>
+        <v>4322.18</v>
       </c>
       <c r="D8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E8" s="73">
         <f t="shared" si="0"/>
-        <v>734.45999999999913</v>
+        <v>771.81999999999971</v>
       </c>
       <c r="F8" s="73">
         <f t="shared" si="6"/>
@@ -6257,15 +6257,15 @@
       </c>
       <c r="G8" s="73">
         <f t="shared" si="7"/>
-        <v>3625.0800000000017</v>
+        <v>3550.3600000000006</v>
       </c>
       <c r="H8" s="72">
         <f t="shared" si="2"/>
-        <v>734.45999999999913</v>
+        <v>771.81999999999971</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="3"/>
-        <v>0.51380647016602654</v>
+        <v>0.50940329695843978</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="4"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="K8" s="73">
         <f t="shared" si="5"/>
-        <v>4125.25</v>
+        <v>4162.6100000000006</v>
       </c>
       <c r="L8" t="s">
         <v>347</v>
@@ -6352,28 +6352,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -6409,7 +6409,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6693,14 +6693,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6710,6 +6702,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6729,20 +6729,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6884,32 +6884,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11357,38 +11357,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C3C68B-BA8D-4C2D-8700-CC0491634AAE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7210AFE-93D3-4C90-B3F7-2B4E53D5E96A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5499,9 +5499,9 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="C8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>4322.18</v>
+        <v>4512.2900000000009</v>
       </c>
       <c r="D8" s="73">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="E8" s="73">
         <f t="shared" si="0"/>
-        <v>771.81999999999971</v>
+        <v>581.70999999999913</v>
       </c>
       <c r="F8" s="73">
         <f t="shared" si="6"/>
@@ -6257,15 +6257,15 @@
       </c>
       <c r="G8" s="73">
         <f t="shared" si="7"/>
-        <v>3550.3600000000006</v>
+        <v>3930.5800000000017</v>
       </c>
       <c r="H8" s="72">
         <f t="shared" si="2"/>
-        <v>771.81999999999971</v>
+        <v>581.70999999999913</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="3"/>
-        <v>0.50940329695843978</v>
+        <v>0.53180927282820201</v>
       </c>
       <c r="J8" s="70">
         <f t="shared" si="4"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="K8" s="73">
         <f t="shared" si="5"/>
-        <v>4162.6100000000006</v>
+        <v>3972.5</v>
       </c>
       <c r="L8" t="s">
         <v>347</v>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>37706.979999999996</v>
+        <v>37897.089999999997</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="E9" s="73">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>20387.590000000004</v>
+        <v>20197.480000000003</v>
       </c>
       <c r="F9" s="73">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -6305,15 +6305,15 @@
       </c>
       <c r="G9" s="73">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>17319.389999999992</v>
+        <v>17699.609999999993</v>
       </c>
       <c r="H9" s="72">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>20387.590000000004</v>
+        <v>20197.480000000003</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.57094278667832765</v>
+        <v>0.57382135009484669</v>
       </c>
       <c r="J9" s="70">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="K9" s="73">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>28336.380000000005</v>
+        <v>28146.270000000004</v>
       </c>
       <c r="L9" t="s">
         <v>347</v>
@@ -6352,28 +6352,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -6409,7 +6409,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6693,6 +6693,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6702,14 +6710,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6729,20 +6729,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6884,32 +6884,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -11357,38 +11357,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
